--- a/experiment/ELAN_bestx3/Test/results_table.xlsx
+++ b/experiment/ELAN_bestx3/Test/results_table.xlsx
@@ -565,43 +565,43 @@
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">
-2,315K</t>
+1,317K</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>28.399/
-0.8219</t>
+          <t>34.417/
+0.9268</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>26.416/
-0.7482</t>
+          <t>30.451/
+0.8444</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>26.268/
-0.7162</t>
+          <t>29.129/
+0.8068</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>23.896/
-0.7142</t>
+          <t>28.354/
+0.8567</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>26.062/
-0.8309</t>
+          <t>33.694/
+0.9452</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>26.208/
-0.7663</t>
+          <t>31.209/
+0.8760</t>
         </is>
       </c>
     </row>
